--- a/examples/example_products.xlsx
+++ b/examples/example_products.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Товары" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -141,56 +141,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>Артикул / SKU</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>Название товара. По нему система пытается определить категорию по файлу data/keyword_rules.xlsx</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>Можно оставить пустым — тогда возьмется модель по умолчанию из настроек.</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>Текущая цена продажи. Если пусто — прибыль и маржа не считаются, но рекомендованная цена считается.</t>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
-      <text>
-        <t>Если заполнено — ручная категория имеет приоритет над автоопределением.</t>
-      </text>
-    </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
-      <text>
-        <t>Опционально: если нужно переопределить хранение для конкретного SKU.</t>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
-      <text>
-        <t>Опционально: если нужно переопределить нашу доставку до склада ЯМ для конкретного SKU (FBY).</t>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
-      <text>
-        <t>Опционально: принудительно указать КГТ.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -480,248 +430,137 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="27" customWidth="1" min="12" max="12"/>
-    <col width="27" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="32" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Артикул</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Product Name</t>
+          <t>Название</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Себестоимость, ₽</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Current Price RUB</t>
+          <t>Вес, кг</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Cost RUB</t>
+          <t>Длина, см</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Weight kg</t>
+          <t>Ширина, см</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Length cm</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Width cm</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Height cm</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Manual Category</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Target Margin % Override</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Storage Cost RUB Override</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Inbound Cost RUB Override</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Is KGT</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Высота, см</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>YM-001</t>
+          <t>TSRD00175588</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Горный велосипед 27.5 алюминий</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>FBY</t>
-        </is>
+          <t>Велосипед горный взрослый 29 дюймов</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>15000</v>
       </c>
       <c r="D2" t="n">
-        <v>32990</v>
+        <v>14.2</v>
       </c>
       <c r="E2" t="n">
-        <v>21500</v>
+        <v>140</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>140</v>
-      </c>
-      <c r="H2" t="n">
-        <v>20</v>
-      </c>
-      <c r="I2" t="n">
         <v>80</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>150</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>пример FBY, наша доставка до склада ЯМ задана по строке</t>
-        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>YM-002</t>
+          <t>DRL000245</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Дрель ударная 810Вт</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>FBS</t>
-        </is>
+          <t>Дрель ударная с кейсом 800 Вт</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3500</v>
       </c>
       <c r="D3" t="n">
-        <v>5490</v>
+        <v>2.1</v>
       </c>
       <c r="E3" t="n">
-        <v>3100</v>
+        <v>35</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>35</v>
-      </c>
-      <c r="H3" t="n">
-        <v>10</v>
-      </c>
-      <c r="I3" t="n">
         <v>25</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>пример FBS</t>
-        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>YM-003</t>
+          <t>SMX1001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Смеситель для ванной латунь</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Смеситель для кухни хром</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1800</v>
+      </c>
       <c r="D4" t="n">
-        <v>7990</v>
+        <v>1.3</v>
       </c>
       <c r="E4" t="n">
-        <v>4200</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>32</v>
-      </c>
-      <c r="H4" t="n">
-        <v>18</v>
-      </c>
-      <c r="I4" t="n">
         <v>8</v>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
-        <v>24</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>пример с target margin override</t>
-        </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="C2:C5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FBS,FBY"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N5000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"TRUE,FALSE"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/examples/example_products.xlsx
+++ b/examples/example_products.xlsx
@@ -450,32 +450,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Название</t>
+          <t>Название товара</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Себестоимость, ₽</t>
+          <t>Себестоимость (руб)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Вес, кг</t>
+          <t>Вес (кг)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Длина, см</t>
+          <t>Длина (см)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Ширина, см</t>
+          <t>Ширина (см)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Высота, см</t>
+          <t>Высота (см)</t>
         </is>
       </c>
     </row>
